--- a/artfynd/A 25021-2022 artfynd.xlsx
+++ b/artfynd/A 25021-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131964</v>
+        <v>122131983</v>
       </c>
       <c r="B2" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563640</v>
+        <v>563623</v>
       </c>
       <c r="R2" t="n">
-        <v>7111532</v>
+        <v>7111498</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132012</v>
+        <v>122131946</v>
       </c>
       <c r="B3" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563643</v>
+        <v>563650</v>
       </c>
       <c r="R3" t="n">
-        <v>7111533</v>
+        <v>7111471</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131944</v>
+        <v>122131990</v>
       </c>
       <c r="B4" t="n">
-        <v>90763</v>
+        <v>98149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563619</v>
+        <v>563656</v>
       </c>
       <c r="R4" t="n">
-        <v>7111462</v>
+        <v>7111467</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131981</v>
+        <v>122132023</v>
       </c>
       <c r="B5" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563643</v>
+        <v>563648</v>
       </c>
       <c r="R5" t="n">
-        <v>7111477</v>
+        <v>7111475</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131983</v>
+        <v>122131964</v>
       </c>
       <c r="B6" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563623</v>
+        <v>563640</v>
       </c>
       <c r="R6" t="n">
-        <v>7111498</v>
+        <v>7111532</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131946</v>
+        <v>122131959</v>
       </c>
       <c r="B7" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563650</v>
+        <v>563609</v>
       </c>
       <c r="R7" t="n">
-        <v>7111471</v>
+        <v>7111468</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122131990</v>
+        <v>122131944</v>
       </c>
       <c r="B8" t="n">
-        <v>98140</v>
+        <v>90772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563656</v>
+        <v>563619</v>
       </c>
       <c r="R8" t="n">
-        <v>7111467</v>
+        <v>7111462</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122132023</v>
+        <v>122131949</v>
       </c>
       <c r="B9" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563648</v>
+        <v>563635</v>
       </c>
       <c r="R9" t="n">
-        <v>7111475</v>
+        <v>7111485</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
         <v>122131945</v>
       </c>
       <c r="B10" t="n">
-        <v>78632</v>
+        <v>78639</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>122132035</v>
       </c>
       <c r="B11" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122131959</v>
+        <v>122132012</v>
       </c>
       <c r="B12" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563609</v>
+        <v>563643</v>
       </c>
       <c r="R12" t="n">
-        <v>7111468</v>
+        <v>7111533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122131949</v>
+        <v>122131981</v>
       </c>
       <c r="B13" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563635</v>
+        <v>563643</v>
       </c>
       <c r="R13" t="n">
-        <v>7111485</v>
+        <v>7111477</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25021-2022 artfynd.xlsx
+++ b/artfynd/A 25021-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131990</v>
+        <v>122131964</v>
       </c>
       <c r="B2" t="n">
         <v>98175</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563656</v>
+        <v>563640</v>
       </c>
       <c r="R2" t="n">
-        <v>7111467</v>
+        <v>7111532</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131964</v>
+        <v>122132012</v>
       </c>
       <c r="B3" t="n">
         <v>98175</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563640</v>
+        <v>563643</v>
       </c>
       <c r="R3" t="n">
-        <v>7111532</v>
+        <v>7111533</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131946</v>
+        <v>122131959</v>
       </c>
       <c r="B4" t="n">
         <v>98175</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563650</v>
+        <v>563609</v>
       </c>
       <c r="R4" t="n">
-        <v>7111471</v>
+        <v>7111468</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131949</v>
+        <v>122131981</v>
       </c>
       <c r="B5" t="n">
         <v>98175</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563635</v>
+        <v>563643</v>
       </c>
       <c r="R5" t="n">
-        <v>7111485</v>
+        <v>7111477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131959</v>
+        <v>122131946</v>
       </c>
       <c r="B6" t="n">
         <v>98175</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563609</v>
+        <v>563650</v>
       </c>
       <c r="R6" t="n">
-        <v>7111468</v>
+        <v>7111471</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122132012</v>
+        <v>122131949</v>
       </c>
       <c r="B7" t="n">
         <v>98175</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563643</v>
+        <v>563635</v>
       </c>
       <c r="R7" t="n">
-        <v>7111533</v>
+        <v>7111485</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122131983</v>
+        <v>122131945</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>78645</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563623</v>
+        <v>563605</v>
       </c>
       <c r="R8" t="n">
-        <v>7111498</v>
+        <v>7111483</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122132035</v>
+        <v>122131990</v>
       </c>
       <c r="B9" t="n">
         <v>98175</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563672</v>
+        <v>563656</v>
       </c>
       <c r="R9" t="n">
-        <v>7111487</v>
+        <v>7111467</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122132023</v>
+        <v>122132035</v>
       </c>
       <c r="B10" t="n">
         <v>98175</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563648</v>
+        <v>563672</v>
       </c>
       <c r="R10" t="n">
-        <v>7111475</v>
+        <v>7111487</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122131981</v>
+        <v>122131944</v>
       </c>
       <c r="B11" t="n">
-        <v>98175</v>
+        <v>90797</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563643</v>
+        <v>563619</v>
       </c>
       <c r="R11" t="n">
-        <v>7111477</v>
+        <v>7111462</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122131944</v>
+        <v>122131983</v>
       </c>
       <c r="B12" t="n">
-        <v>90797</v>
+        <v>98175</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563619</v>
+        <v>563623</v>
       </c>
       <c r="R12" t="n">
-        <v>7111462</v>
+        <v>7111498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122131945</v>
+        <v>122132023</v>
       </c>
       <c r="B13" t="n">
-        <v>78645</v>
+        <v>98175</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563605</v>
+        <v>563648</v>
       </c>
       <c r="R13" t="n">
-        <v>7111483</v>
+        <v>7111475</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25021-2022 artfynd.xlsx
+++ b/artfynd/A 25021-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131964</v>
+        <v>122132023</v>
       </c>
       <c r="B2" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563640</v>
+        <v>563648</v>
       </c>
       <c r="R2" t="n">
-        <v>7111532</v>
+        <v>7111475</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132012</v>
+        <v>122131949</v>
       </c>
       <c r="B3" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563643</v>
+        <v>563635</v>
       </c>
       <c r="R3" t="n">
-        <v>7111533</v>
+        <v>7111485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131959</v>
+        <v>122132035</v>
       </c>
       <c r="B4" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563609</v>
+        <v>563672</v>
       </c>
       <c r="R4" t="n">
-        <v>7111468</v>
+        <v>7111487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131981</v>
+        <v>122132012</v>
       </c>
       <c r="B5" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>563643</v>
       </c>
       <c r="R5" t="n">
-        <v>7111477</v>
+        <v>7111533</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131946</v>
+        <v>122131990</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563650</v>
+        <v>563656</v>
       </c>
       <c r="R6" t="n">
-        <v>7111471</v>
+        <v>7111467</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131949</v>
+        <v>122131959</v>
       </c>
       <c r="B7" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563635</v>
+        <v>563609</v>
       </c>
       <c r="R7" t="n">
-        <v>7111485</v>
+        <v>7111468</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
         <v>122131945</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131990</v>
+        <v>122131946</v>
       </c>
       <c r="B9" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563656</v>
+        <v>563650</v>
       </c>
       <c r="R9" t="n">
-        <v>7111467</v>
+        <v>7111471</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122132035</v>
+        <v>122131944</v>
       </c>
       <c r="B10" t="n">
-        <v>98175</v>
+        <v>90807</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563672</v>
+        <v>563619</v>
       </c>
       <c r="R10" t="n">
-        <v>7111487</v>
+        <v>7111462</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122131944</v>
+        <v>122131981</v>
       </c>
       <c r="B11" t="n">
-        <v>90797</v>
+        <v>98185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563619</v>
+        <v>563643</v>
       </c>
       <c r="R11" t="n">
-        <v>7111462</v>
+        <v>7111477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
         <v>122131983</v>
       </c>
       <c r="B12" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122132023</v>
+        <v>122131964</v>
       </c>
       <c r="B13" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563648</v>
+        <v>563640</v>
       </c>
       <c r="R13" t="n">
-        <v>7111475</v>
+        <v>7111532</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25021-2022 artfynd.xlsx
+++ b/artfynd/A 25021-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132023</v>
+        <v>122131983</v>
       </c>
       <c r="B2" t="n">
         <v>98185</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563648</v>
+        <v>563623</v>
       </c>
       <c r="R2" t="n">
-        <v>7111475</v>
+        <v>7111498</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131949</v>
+        <v>122132012</v>
       </c>
       <c r="B3" t="n">
         <v>98185</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563635</v>
+        <v>563643</v>
       </c>
       <c r="R3" t="n">
-        <v>7111485</v>
+        <v>7111533</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132035</v>
+        <v>122131959</v>
       </c>
       <c r="B4" t="n">
         <v>98185</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563672</v>
+        <v>563609</v>
       </c>
       <c r="R4" t="n">
-        <v>7111487</v>
+        <v>7111468</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122132012</v>
+        <v>122131944</v>
       </c>
       <c r="B5" t="n">
-        <v>98185</v>
+        <v>90807</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563643</v>
+        <v>563619</v>
       </c>
       <c r="R5" t="n">
-        <v>7111533</v>
+        <v>7111462</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131990</v>
+        <v>122131949</v>
       </c>
       <c r="B6" t="n">
         <v>98185</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563656</v>
+        <v>563635</v>
       </c>
       <c r="R6" t="n">
-        <v>7111467</v>
+        <v>7111485</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131959</v>
+        <v>122131945</v>
       </c>
       <c r="B7" t="n">
-        <v>98185</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563609</v>
+        <v>563605</v>
       </c>
       <c r="R7" t="n">
-        <v>7111468</v>
+        <v>7111483</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122131945</v>
+        <v>122132023</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563605</v>
+        <v>563648</v>
       </c>
       <c r="R8" t="n">
-        <v>7111483</v>
+        <v>7111475</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131946</v>
+        <v>122131964</v>
       </c>
       <c r="B9" t="n">
         <v>98185</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563650</v>
+        <v>563640</v>
       </c>
       <c r="R9" t="n">
-        <v>7111471</v>
+        <v>7111532</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122131944</v>
+        <v>122132035</v>
       </c>
       <c r="B10" t="n">
-        <v>90807</v>
+        <v>98185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563619</v>
+        <v>563672</v>
       </c>
       <c r="R10" t="n">
-        <v>7111462</v>
+        <v>7111487</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122131983</v>
+        <v>122131946</v>
       </c>
       <c r="B12" t="n">
         <v>98185</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563623</v>
+        <v>563650</v>
       </c>
       <c r="R12" t="n">
-        <v>7111498</v>
+        <v>7111471</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122131964</v>
+        <v>122131990</v>
       </c>
       <c r="B13" t="n">
         <v>98185</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563640</v>
+        <v>563656</v>
       </c>
       <c r="R13" t="n">
-        <v>7111532</v>
+        <v>7111467</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25021-2022 artfynd.xlsx
+++ b/artfynd/A 25021-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131983</v>
+        <v>122132023</v>
       </c>
       <c r="B2" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563623</v>
+        <v>563648</v>
       </c>
       <c r="R2" t="n">
-        <v>7111498</v>
+        <v>7111475</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132012</v>
+        <v>122132035</v>
       </c>
       <c r="B3" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563643</v>
+        <v>563672</v>
       </c>
       <c r="R3" t="n">
-        <v>7111533</v>
+        <v>7111487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131959</v>
+        <v>122131981</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563609</v>
+        <v>563643</v>
       </c>
       <c r="R4" t="n">
-        <v>7111468</v>
+        <v>7111477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131944</v>
+        <v>122131983</v>
       </c>
       <c r="B5" t="n">
-        <v>90807</v>
+        <v>98197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563619</v>
+        <v>563623</v>
       </c>
       <c r="R5" t="n">
-        <v>7111462</v>
+        <v>7111498</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131949</v>
+        <v>122132012</v>
       </c>
       <c r="B6" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563635</v>
+        <v>563643</v>
       </c>
       <c r="R6" t="n">
-        <v>7111485</v>
+        <v>7111533</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131945</v>
+        <v>122131964</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>98197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563605</v>
+        <v>563640</v>
       </c>
       <c r="R7" t="n">
-        <v>7111483</v>
+        <v>7111532</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122132023</v>
+        <v>122131959</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563648</v>
+        <v>563609</v>
       </c>
       <c r="R8" t="n">
-        <v>7111475</v>
+        <v>7111468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131964</v>
+        <v>122131945</v>
       </c>
       <c r="B9" t="n">
-        <v>98185</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563640</v>
+        <v>563605</v>
       </c>
       <c r="R9" t="n">
-        <v>7111532</v>
+        <v>7111483</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122132035</v>
+        <v>122131946</v>
       </c>
       <c r="B10" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563672</v>
+        <v>563650</v>
       </c>
       <c r="R10" t="n">
-        <v>7111487</v>
+        <v>7111471</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122131981</v>
+        <v>122131949</v>
       </c>
       <c r="B11" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563643</v>
+        <v>563635</v>
       </c>
       <c r="R11" t="n">
-        <v>7111477</v>
+        <v>7111485</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122131946</v>
+        <v>122131944</v>
       </c>
       <c r="B12" t="n">
-        <v>98185</v>
+        <v>90819</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563650</v>
+        <v>563619</v>
       </c>
       <c r="R12" t="n">
-        <v>7111471</v>
+        <v>7111462</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
         <v>122131990</v>
       </c>
       <c r="B13" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 25021-2022 artfynd.xlsx
+++ b/artfynd/A 25021-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132023</v>
+        <v>122131983</v>
       </c>
       <c r="B2" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563648</v>
+        <v>563623</v>
       </c>
       <c r="R2" t="n">
-        <v>7111475</v>
+        <v>7111498</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132035</v>
+        <v>122131990</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563672</v>
+        <v>563656</v>
       </c>
       <c r="R3" t="n">
-        <v>7111487</v>
+        <v>7111467</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131981</v>
+        <v>122131959</v>
       </c>
       <c r="B4" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563643</v>
+        <v>563609</v>
       </c>
       <c r="R4" t="n">
-        <v>7111477</v>
+        <v>7111468</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131983</v>
+        <v>122131981</v>
       </c>
       <c r="B5" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563623</v>
+        <v>563643</v>
       </c>
       <c r="R5" t="n">
-        <v>7111498</v>
+        <v>7111477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122132012</v>
+        <v>122131946</v>
       </c>
       <c r="B6" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563643</v>
+        <v>563650</v>
       </c>
       <c r="R6" t="n">
-        <v>7111533</v>
+        <v>7111471</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>122131964</v>
       </c>
       <c r="B7" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122131959</v>
+        <v>122131945</v>
       </c>
       <c r="B8" t="n">
-        <v>98197</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563609</v>
+        <v>563605</v>
       </c>
       <c r="R8" t="n">
-        <v>7111468</v>
+        <v>7111483</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131945</v>
+        <v>122132035</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563605</v>
+        <v>563672</v>
       </c>
       <c r="R9" t="n">
-        <v>7111483</v>
+        <v>7111487</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122131946</v>
+        <v>122131949</v>
       </c>
       <c r="B10" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563650</v>
+        <v>563635</v>
       </c>
       <c r="R10" t="n">
-        <v>7111471</v>
+        <v>7111485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122131949</v>
+        <v>122132012</v>
       </c>
       <c r="B11" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563635</v>
+        <v>563643</v>
       </c>
       <c r="R11" t="n">
-        <v>7111485</v>
+        <v>7111533</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122131944</v>
+        <v>122132023</v>
       </c>
       <c r="B12" t="n">
-        <v>90819</v>
+        <v>98202</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563619</v>
+        <v>563648</v>
       </c>
       <c r="R12" t="n">
-        <v>7111462</v>
+        <v>7111475</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122131990</v>
+        <v>122131944</v>
       </c>
       <c r="B13" t="n">
-        <v>98197</v>
+        <v>90826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563656</v>
+        <v>563619</v>
       </c>
       <c r="R13" t="n">
-        <v>7111467</v>
+        <v>7111462</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25021-2022 artfynd.xlsx
+++ b/artfynd/A 25021-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122131983</v>
       </c>
       <c r="B2" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131990</v>
+        <v>122132023</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,11 +790,6 @@
       <c r="E3" t="n">
         <v>220787</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563656</v>
+        <v>563648</v>
       </c>
       <c r="R3" t="n">
-        <v>7111467</v>
+        <v>7111475</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131959</v>
+        <v>122131981</v>
       </c>
       <c r="B4" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,11 +887,6 @@
       <c r="E4" t="n">
         <v>220787</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563609</v>
+        <v>563643</v>
       </c>
       <c r="R4" t="n">
-        <v>7111468</v>
+        <v>7111477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131981</v>
+        <v>122132012</v>
       </c>
       <c r="B5" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,11 +984,6 @@
       <c r="E5" t="n">
         <v>220787</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1024,7 +1004,7 @@
         <v>563643</v>
       </c>
       <c r="R5" t="n">
-        <v>7111477</v>
+        <v>7111533</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131946</v>
+        <v>122131959</v>
       </c>
       <c r="B6" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,11 +1081,6 @@
       <c r="E6" t="n">
         <v>220787</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563650</v>
+        <v>563609</v>
       </c>
       <c r="R6" t="n">
-        <v>7111471</v>
+        <v>7111468</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131964</v>
+        <v>122131990</v>
       </c>
       <c r="B7" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1203,11 +1178,6 @@
       <c r="E7" t="n">
         <v>220787</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563640</v>
+        <v>563656</v>
       </c>
       <c r="R7" t="n">
-        <v>7111532</v>
+        <v>7111467</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1260,7 @@
         <v>122131945</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,11 +1274,6 @@
       </c>
       <c r="E8" t="n">
         <v>6425</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1389,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122132035</v>
+        <v>122131946</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1407,11 +1372,6 @@
       <c r="E9" t="n">
         <v>220787</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563672</v>
+        <v>563650</v>
       </c>
       <c r="R9" t="n">
-        <v>7111487</v>
+        <v>7111471</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1454,7 @@
         <v>122131949</v>
       </c>
       <c r="B10" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,11 +1468,6 @@
       </c>
       <c r="E10" t="n">
         <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1593,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122132012</v>
+        <v>122132035</v>
       </c>
       <c r="B11" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1611,11 +1566,6 @@
       <c r="E11" t="n">
         <v>220787</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563643</v>
+        <v>563672</v>
       </c>
       <c r="R11" t="n">
-        <v>7111533</v>
+        <v>7111487</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122132023</v>
+        <v>122131964</v>
       </c>
       <c r="B12" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1713,11 +1663,6 @@
       <c r="E12" t="n">
         <v>220787</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563648</v>
+        <v>563640</v>
       </c>
       <c r="R12" t="n">
-        <v>7111475</v>
+        <v>7111532</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1745,7 @@
         <v>122131944</v>
       </c>
       <c r="B13" t="n">
-        <v>90826</v>
+        <v>90831</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,11 +1759,6 @@
       </c>
       <c r="E13" t="n">
         <v>5432</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>

--- a/artfynd/A 25021-2022 artfynd.xlsx
+++ b/artfynd/A 25021-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122131983</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132023</v>
+        <v>122131990</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,6 +795,11 @@
       <c r="E3" t="n">
         <v>220787</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563648</v>
+        <v>563656</v>
       </c>
       <c r="R3" t="n">
-        <v>7111475</v>
+        <v>7111467</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131981</v>
+        <v>122131964</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -887,6 +897,11 @@
       <c r="E4" t="n">
         <v>220787</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -904,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563643</v>
+        <v>563640</v>
       </c>
       <c r="R4" t="n">
-        <v>7111477</v>
+        <v>7111532</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122132012</v>
+        <v>122131959</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -984,6 +999,11 @@
       <c r="E5" t="n">
         <v>220787</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1001,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563643</v>
+        <v>563609</v>
       </c>
       <c r="R5" t="n">
-        <v>7111533</v>
+        <v>7111468</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131959</v>
+        <v>122131946</v>
       </c>
       <c r="B6" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1081,6 +1101,11 @@
       <c r="E6" t="n">
         <v>220787</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1098,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563609</v>
+        <v>563650</v>
       </c>
       <c r="R6" t="n">
-        <v>7111468</v>
+        <v>7111471</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131990</v>
+        <v>122131949</v>
       </c>
       <c r="B7" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1178,6 +1203,11 @@
       <c r="E7" t="n">
         <v>220787</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1195,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563656</v>
+        <v>563635</v>
       </c>
       <c r="R7" t="n">
-        <v>7111467</v>
+        <v>7111485</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122131945</v>
+        <v>122131981</v>
       </c>
       <c r="B8" t="n">
-        <v>78652</v>
+        <v>98224</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1269,20 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563605</v>
+        <v>563643</v>
       </c>
       <c r="R8" t="n">
-        <v>7111483</v>
+        <v>7111477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131946</v>
+        <v>122132012</v>
       </c>
       <c r="B9" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1372,6 +1407,11 @@
       <c r="E9" t="n">
         <v>220787</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1389,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563650</v>
+        <v>563643</v>
       </c>
       <c r="R9" t="n">
-        <v>7111471</v>
+        <v>7111533</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122131949</v>
+        <v>122132023</v>
       </c>
       <c r="B10" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1469,6 +1509,11 @@
       <c r="E10" t="n">
         <v>220787</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1486,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563635</v>
+        <v>563648</v>
       </c>
       <c r="R10" t="n">
-        <v>7111485</v>
+        <v>7111475</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122132035</v>
+        <v>122131944</v>
       </c>
       <c r="B11" t="n">
-        <v>98211</v>
+        <v>90844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1560,20 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563672</v>
+        <v>563619</v>
       </c>
       <c r="R11" t="n">
-        <v>7111487</v>
+        <v>7111462</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122131964</v>
+        <v>122131945</v>
       </c>
       <c r="B12" t="n">
-        <v>98211</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1657,20 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563640</v>
+        <v>563605</v>
       </c>
       <c r="R12" t="n">
-        <v>7111532</v>
+        <v>7111483</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122131944</v>
+        <v>122132035</v>
       </c>
       <c r="B13" t="n">
-        <v>90831</v>
+        <v>98224</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1754,20 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563619</v>
+        <v>563672</v>
       </c>
       <c r="R13" t="n">
-        <v>7111462</v>
+        <v>7111487</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25021-2022 artfynd.xlsx
+++ b/artfynd/A 25021-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131983</v>
+        <v>122132012</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563623</v>
+        <v>563643</v>
       </c>
       <c r="R2" t="n">
-        <v>7111498</v>
+        <v>7111533</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131990</v>
+        <v>122131945</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563656</v>
+        <v>563605</v>
       </c>
       <c r="R3" t="n">
-        <v>7111467</v>
+        <v>7111483</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131964</v>
+        <v>122131983</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563640</v>
+        <v>563623</v>
       </c>
       <c r="R4" t="n">
-        <v>7111532</v>
+        <v>7111498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131959</v>
+        <v>122131990</v>
       </c>
       <c r="B5" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563609</v>
+        <v>563656</v>
       </c>
       <c r="R5" t="n">
-        <v>7111468</v>
+        <v>7111467</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131946</v>
+        <v>122131959</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563650</v>
+        <v>563609</v>
       </c>
       <c r="R6" t="n">
-        <v>7111471</v>
+        <v>7111468</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131949</v>
+        <v>122131946</v>
       </c>
       <c r="B7" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563635</v>
+        <v>563650</v>
       </c>
       <c r="R7" t="n">
-        <v>7111485</v>
+        <v>7111471</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122131981</v>
+        <v>122132035</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563643</v>
+        <v>563672</v>
       </c>
       <c r="R8" t="n">
-        <v>7111477</v>
+        <v>7111487</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122132012</v>
+        <v>122131964</v>
       </c>
       <c r="B9" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563643</v>
+        <v>563640</v>
       </c>
       <c r="R9" t="n">
-        <v>7111533</v>
+        <v>7111532</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122132023</v>
+        <v>122131949</v>
       </c>
       <c r="B10" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563648</v>
+        <v>563635</v>
       </c>
       <c r="R10" t="n">
-        <v>7111475</v>
+        <v>7111485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122131944</v>
+        <v>122132023</v>
       </c>
       <c r="B11" t="n">
-        <v>90844</v>
+        <v>98237</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563619</v>
+        <v>563648</v>
       </c>
       <c r="R11" t="n">
-        <v>7111462</v>
+        <v>7111475</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122131945</v>
+        <v>122131944</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>90857</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563605</v>
+        <v>563619</v>
       </c>
       <c r="R12" t="n">
-        <v>7111483</v>
+        <v>7111462</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122132035</v>
+        <v>122131981</v>
       </c>
       <c r="B13" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563672</v>
+        <v>563643</v>
       </c>
       <c r="R13" t="n">
-        <v>7111487</v>
+        <v>7111477</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 25021-2022 artfynd.xlsx
+++ b/artfynd/A 25021-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132012</v>
+        <v>122131945</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563643</v>
+        <v>563605</v>
       </c>
       <c r="R2" t="n">
-        <v>7111533</v>
+        <v>7111483</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131945</v>
+        <v>122131946</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563605</v>
+        <v>563650</v>
       </c>
       <c r="R3" t="n">
-        <v>7111483</v>
+        <v>7111471</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131983</v>
+        <v>122131949</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563623</v>
+        <v>563635</v>
       </c>
       <c r="R4" t="n">
-        <v>7111498</v>
+        <v>7111485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131990</v>
+        <v>122131959</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563656</v>
+        <v>563609</v>
       </c>
       <c r="R5" t="n">
-        <v>7111467</v>
+        <v>7111468</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131959</v>
+        <v>122131964</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563609</v>
+        <v>563640</v>
       </c>
       <c r="R6" t="n">
-        <v>7111468</v>
+        <v>7111532</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131946</v>
+        <v>122131981</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563650</v>
+        <v>563643</v>
       </c>
       <c r="R7" t="n">
-        <v>7111471</v>
+        <v>7111477</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122132035</v>
+        <v>122131983</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563672</v>
+        <v>563623</v>
       </c>
       <c r="R8" t="n">
-        <v>7111487</v>
+        <v>7111498</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131964</v>
+        <v>122131986</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563640</v>
+        <v>563625</v>
       </c>
       <c r="R9" t="n">
-        <v>7111532</v>
+        <v>7111439</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122131949</v>
+        <v>122131990</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563635</v>
+        <v>563656</v>
       </c>
       <c r="R10" t="n">
-        <v>7111485</v>
+        <v>7111467</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122132023</v>
+        <v>122132008</v>
       </c>
       <c r="B11" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563648</v>
+        <v>563638</v>
       </c>
       <c r="R11" t="n">
-        <v>7111475</v>
+        <v>7111429</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122131944</v>
+        <v>122132012</v>
       </c>
       <c r="B12" t="n">
-        <v>90857</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563619</v>
+        <v>563643</v>
       </c>
       <c r="R12" t="n">
-        <v>7111462</v>
+        <v>7111533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122131981</v>
+        <v>122132023</v>
       </c>
       <c r="B13" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563643</v>
+        <v>563648</v>
       </c>
       <c r="R13" t="n">
-        <v>7111477</v>
+        <v>7111475</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,6 +1836,103 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122132035</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Valberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>563672</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7111487</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25021-2022 artfynd.xlsx
+++ b/artfynd/A 25021-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131945</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131946</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131949</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131959</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131964</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131981</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131983</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131986</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131990</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122132008</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122132012</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122132023</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,8 +1998,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122132035</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>